--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tuenl-my.sharepoint.com/personal/f_nardella_student_tue_nl/Documents/INNO Energy/UPC Energy Policy/TIMES_ses/MSc_SELECT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juane\Documents\Master UPC\2 Energy Modelling and Climate Policy\TIMES Project\Msc_SELECT_VEDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{13D91245-91CE-4E87-951E-9ABEA10B1F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD770827-29AB-40B2-BFE0-E7FECA6538BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC3850A-D53C-443A-AA8D-659F3C35CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="402">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1266,6 +1266,12 @@
   </si>
   <si>
     <t>4W7SU8</t>
+  </si>
+  <si>
+    <t>….................</t>
+  </si>
+  <si>
+    <t>COST~1</t>
   </si>
 </sst>
 </file>
@@ -3415,7 +3421,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3491,6 +3497,7 @@
     <xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="50" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" xfId="724" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="726">
     <cellStyle name="20 % - Akzent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3947,6 +3954,7 @@
     <cellStyle name="Neutralne 8" xfId="452" xr:uid="{00000000-0005-0000-0000-0000C3010000}"/>
     <cellStyle name="Neutralne 9" xfId="453" xr:uid="{00000000-0005-0000-0000-0000C4010000}"/>
     <cellStyle name="no dec" xfId="454" xr:uid="{00000000-0005-0000-0000-0000C5010000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="455" xr:uid="{00000000-0005-0000-0000-0000C6010000}"/>
     <cellStyle name="Normal 10" xfId="456" xr:uid="{00000000-0005-0000-0000-0000C7010000}"/>
     <cellStyle name="Normal 10 2" xfId="723" xr:uid="{EB0C2ED4-4687-4FED-8497-A80B55395A75}"/>
@@ -3970,7 +3978,6 @@
     <cellStyle name="Normal GHG-Shade" xfId="473" xr:uid="{00000000-0005-0000-0000-0000D8010000}"/>
     <cellStyle name="Normal GHG-Shade 2" xfId="474" xr:uid="{00000000-0005-0000-0000-0000D9010000}"/>
     <cellStyle name="Normal_Constants 2" xfId="722" xr:uid="{C6AA90A5-1043-4AB8-B229-DB93742915B6}"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
     <cellStyle name="Normalny 10" xfId="475" xr:uid="{00000000-0005-0000-0000-0000DD010000}"/>
     <cellStyle name="Normalny 10 2" xfId="476" xr:uid="{00000000-0005-0000-0000-0000DE010000}"/>
     <cellStyle name="Normalny 11" xfId="477" xr:uid="{00000000-0005-0000-0000-0000DF010000}"/>
@@ -10282,7 +10289,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C8BD73-0DF8-4F72-B0F0-D4FB13B1EA60}">
-  <dimension ref="B2:D4"/>
+  <dimension ref="B2:J40"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="38"/>
@@ -10310,15 +10317,31 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.8" thickBot="1">
-      <c r="B4" s="40" t="s">
+    <row r="4" spans="2:4">
+      <c r="B4" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="57">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="13.8" thickBot="1">
+      <c r="B5" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="10:10">
+      <c r="J40" s="38" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -10327,21 +10350,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E800C01780957C4993EAD0B0EDC5E8FF" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1ada55d1baadc38a59b37f146ad1da21">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="95645557-b925-4e14-b9c3-bb0dccab904e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a6148ddbe210b331c9edc42bf7e0f90a" ns2:_="">
     <xsd:import namespace="95645557-b925-4e14-b9c3-bb0dccab904e"/>
@@ -10485,31 +10493,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641C9249-69FC-4D80-A8BF-F45CF9C8F019}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="95645557-b925-4e14-b9c3-bb0dccab904e"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF4A66DF-54A6-4E03-963C-8A735A5B845A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38EE394D-E8DA-413E-B5EF-6DF7212C84CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10525,4 +10524,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF4A66DF-54A6-4E03-963C-8A735A5B845A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{641C9249-69FC-4D80-A8BF-F45CF9C8F019}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="95645557-b925-4e14-b9c3-bb0dccab904e"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>